--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -757,12 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123307520</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,135 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128725191</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56615</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567548</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6509541</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128725191</v>
       </c>
       <c r="B3" t="n">
-        <v>56615</v>
+        <v>56642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128725191</v>
       </c>
       <c r="B3" t="n">
-        <v>56642</v>
+        <v>56645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128725191</v>
       </c>
       <c r="B3" t="n">
-        <v>56645</v>
+        <v>56648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128725191</v>
       </c>
       <c r="B3" t="n">
-        <v>56648</v>
+        <v>56650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128725191</v>
       </c>
       <c r="B3" t="n">
-        <v>56650</v>
+        <v>56652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,224 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129403662</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92860</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6509539</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129403649</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6509539</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>129403662</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129403649</v>
       </c>
       <c r="B5" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>131191459</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131257158</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>131191459</v>
       </c>
       <c r="B6" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131257158</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>131191459</v>
       </c>
       <c r="B6" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131257158</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131527895</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,124 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131713039</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,6 +1578,115 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131765843</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58546</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6509570</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131257158</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131527895</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>131713039</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131257158</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131527895</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>131713039</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131765843</v>
       </c>
       <c r="B10" t="n">
-        <v>58546</v>
+        <v>58549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,69 +800,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128725191</v>
+        <v>127679939</v>
       </c>
       <c r="B3" t="n">
-        <v>56652</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567548</v>
+        <v>567571</v>
       </c>
       <c r="R3" t="n">
-        <v>6509541</v>
+        <v>6509585</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,59 +920,69 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129403662</v>
+        <v>128725191</v>
       </c>
       <c r="B4" t="n">
-        <v>92919</v>
+        <v>56652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567445</v>
+        <v>567548</v>
       </c>
       <c r="R4" t="n">
-        <v>6509539</v>
+        <v>6509541</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,12 +1006,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,37 +1049,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403649</v>
+        <v>129403662</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1147,42 +1158,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131191459</v>
+        <v>129403649</v>
       </c>
       <c r="B6" t="n">
-        <v>58057</v>
+        <v>92881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567527</v>
+        <v>567445</v>
       </c>
       <c r="R6" t="n">
-        <v>6509582</v>
+        <v>6509539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,12 +1234,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,6 +1248,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257158</v>
+        <v>131191459</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,7 +1300,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1295,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567581</v>
+        <v>567527</v>
       </c>
       <c r="R7" t="n">
-        <v>6509575</v>
+        <v>6509582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,12 +1340,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131527895</v>
+        <v>131257158</v>
       </c>
       <c r="B8" t="n">
         <v>57899</v>
@@ -1400,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567425</v>
+        <v>567581</v>
       </c>
       <c r="R8" t="n">
-        <v>6509535</v>
+        <v>6509575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,12 +1445,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131713039</v>
+        <v>131527895</v>
       </c>
       <c r="B9" t="n">
         <v>57899</v>
@@ -1490,20 +1505,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1513,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567414</v>
+        <v>567425</v>
       </c>
       <c r="R9" t="n">
-        <v>6509506</v>
+        <v>6509535</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,17 +1550,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,27 +1582,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131765843</v>
+        <v>131713039</v>
       </c>
       <c r="B10" t="n">
-        <v>58549</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1610,14 +1612,18 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1627,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567553</v>
+        <v>567414</v>
       </c>
       <c r="R10" t="n">
-        <v>6509570</v>
+        <v>6509506</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1657,12 +1663,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,6 +1697,321 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131765843</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58549</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567553</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6509570</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131861026</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91853</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567581</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6509590</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131861151</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58549</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567468</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6509548</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127679939</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131527895</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>131713039</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>131765843</v>
       </c>
       <c r="B11" t="n">
-        <v>58549</v>
+        <v>58551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>131861026</v>
       </c>
       <c r="B12" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>131861151</v>
       </c>
       <c r="B13" t="n">
-        <v>58549</v>
+        <v>58551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +803,7 @@
         <v>127679939</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131527895</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>131713039</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>131765843</v>
       </c>
       <c r="B11" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>131861026</v>
       </c>
       <c r="B12" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>131861151</v>
       </c>
       <c r="B13" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,6 +2012,216 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132110067</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58588</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567468</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6509548</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132110198</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58588</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567553</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6509570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127679939</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131527895</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>131713039</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>131765843</v>
       </c>
       <c r="B11" t="n">
-        <v>58554</v>
+        <v>58559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>131861026</v>
       </c>
       <c r="B12" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>131861151</v>
       </c>
       <c r="B13" t="n">
-        <v>58554</v>
+        <v>58559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>132110067</v>
       </c>
       <c r="B14" t="n">
-        <v>58588</v>
+        <v>58593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>132110198</v>
       </c>
       <c r="B15" t="n">
-        <v>58588</v>
+        <v>58593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +803,7 @@
         <v>127679939</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>131765843</v>
       </c>
       <c r="B11" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>131861026</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>131861151</v>
       </c>
       <c r="B13" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>132110067</v>
       </c>
       <c r="B14" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>132110198</v>
       </c>
       <c r="B15" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>132333380</v>
       </c>
       <c r="B16" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,6 +2324,230 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132455583</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58322</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567548</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6509541</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132455861</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58631</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567548</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6509541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132110067</v>
+        <v>132110198</v>
       </c>
       <c r="B14" t="n">
         <v>58631</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R14" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,7 +2120,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B15" t="n">
         <v>58631</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R15" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B14" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R14" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132110067</v>
+        <v>132110198</v>
       </c>
       <c r="B15" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R15" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,7 +2228,7 @@
         <v>132333380</v>
       </c>
       <c r="B16" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>132455583</v>
       </c>
       <c r="B17" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>132455861</v>
       </c>
       <c r="B18" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2018,7 +2018,7 @@
         <v>132110067</v>
       </c>
       <c r="B14" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>132110198</v>
       </c>
       <c r="B15" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>132333380</v>
       </c>
       <c r="B16" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>132455583</v>
       </c>
       <c r="B17" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>132455861</v>
       </c>
       <c r="B18" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2548,6 +2548,434 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132863077</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58603</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567541</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6509560</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132863110</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567541</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6509560</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132863104</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567541</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6509560</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132863200</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58440</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567541</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6509560</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132110067</v>
+        <v>132110198</v>
       </c>
       <c r="B14" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R14" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B15" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R15" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,7 +2228,7 @@
         <v>132333380</v>
       </c>
       <c r="B16" t="n">
-        <v>58497</v>
+        <v>58498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>132455583</v>
       </c>
       <c r="B17" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>132455861</v>
       </c>
       <c r="B18" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B14" t="n">
         <v>58637</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R14" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,7 +2120,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132110067</v>
+        <v>132110198</v>
       </c>
       <c r="B15" t="n">
         <v>58637</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R15" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +2976,1056 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133035527</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58498</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567542</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6509592</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133035510</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58440</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567542</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6509592</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133036139</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567542</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6509592</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133034484</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58440</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133035361</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58440</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567468</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6509548</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133036146</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>567542</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6509592</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133034592</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58498</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133034492</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133034467</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133034573</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58113</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>567414</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6509506</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2865,48 +2865,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132863200</v>
+        <v>133035527</v>
       </c>
       <c r="B22" t="n">
-        <v>58440</v>
+        <v>58498</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2916,10 +2908,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567541</v>
+        <v>567542</v>
       </c>
       <c r="R22" t="n">
-        <v>6509560</v>
+        <v>6509592</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2946,12 +2938,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,32 +2970,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133035527</v>
+        <v>133035510</v>
       </c>
       <c r="B23" t="n">
-        <v>58498</v>
+        <v>58440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,32 +3075,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133035510</v>
+        <v>133036139</v>
       </c>
       <c r="B24" t="n">
-        <v>58440</v>
+        <v>58328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3156,12 +3148,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,32 +3180,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133036139</v>
+        <v>133034484</v>
       </c>
       <c r="B25" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3231,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R25" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3261,12 +3253,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,7 +3285,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133034484</v>
+        <v>133035361</v>
       </c>
       <c r="B26" t="n">
         <v>58440</v>
@@ -3336,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R26" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3366,12 +3358,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,32 +3390,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133035361</v>
+        <v>133036146</v>
       </c>
       <c r="B27" t="n">
-        <v>58440</v>
+        <v>58637</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3441,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R27" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3471,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3503,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133036146</v>
+        <v>133034592</v>
       </c>
       <c r="B28" t="n">
-        <v>58637</v>
+        <v>58498</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3514,16 +3506,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3536,7 +3528,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3546,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R28" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3576,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,10 +3600,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133034592</v>
+        <v>133034492</v>
       </c>
       <c r="B29" t="n">
-        <v>58498</v>
+        <v>58637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,16 +3611,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3641,7 +3633,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3713,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034492</v>
+        <v>133034467</v>
       </c>
       <c r="B30" t="n">
-        <v>58637</v>
+        <v>58328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,16 +3716,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3818,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B31" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3861,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B30" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B31" t="n">
-        <v>58440</v>
+        <v>58328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B30" t="n">
-        <v>58440</v>
+        <v>58328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B31" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3285,32 +3285,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133035361</v>
+        <v>133036146</v>
       </c>
       <c r="B26" t="n">
-        <v>58440</v>
+        <v>58637</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R26" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,32 +3390,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133036146</v>
+        <v>133035361</v>
       </c>
       <c r="B27" t="n">
-        <v>58637</v>
+        <v>58440</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R27" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B30" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B31" t="n">
-        <v>58440</v>
+        <v>58328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3285,32 +3285,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133036146</v>
+        <v>133035361</v>
       </c>
       <c r="B26" t="n">
-        <v>58637</v>
+        <v>58440</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R26" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,32 +3390,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133035361</v>
+        <v>133036146</v>
       </c>
       <c r="B27" t="n">
-        <v>58440</v>
+        <v>58637</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R27" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B30" t="n">
-        <v>58440</v>
+        <v>58328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B31" t="n">
-        <v>58328</v>
+        <v>58440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2865,32 +2865,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133035527</v>
+        <v>133035510</v>
       </c>
       <c r="B22" t="n">
-        <v>58498</v>
+        <v>58440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133035510</v>
+        <v>133035527</v>
       </c>
       <c r="B23" t="n">
-        <v>58440</v>
+        <v>58498</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2228,7 +2228,7 @@
         <v>132333380</v>
       </c>
       <c r="B16" t="n">
-        <v>58498</v>
+        <v>58501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>132455583</v>
       </c>
       <c r="B17" t="n">
-        <v>58328</v>
+        <v>58331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>132455861</v>
       </c>
       <c r="B18" t="n">
-        <v>58637</v>
+        <v>58640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>132863077</v>
       </c>
       <c r="B19" t="n">
-        <v>58603</v>
+        <v>58606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>132863110</v>
       </c>
       <c r="B20" t="n">
-        <v>58328</v>
+        <v>58331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>132863104</v>
       </c>
       <c r="B21" t="n">
-        <v>58637</v>
+        <v>58640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>133035510</v>
       </c>
       <c r="B22" t="n">
-        <v>58440</v>
+        <v>58443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>133035527</v>
       </c>
       <c r="B23" t="n">
-        <v>58498</v>
+        <v>58501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>133036139</v>
       </c>
       <c r="B24" t="n">
-        <v>58328</v>
+        <v>58331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>133034484</v>
       </c>
       <c r="B25" t="n">
-        <v>58440</v>
+        <v>58443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133035361</v>
+        <v>133036146</v>
       </c>
       <c r="B26" t="n">
-        <v>58440</v>
+        <v>58640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R26" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,32 +3390,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133036146</v>
+        <v>133035361</v>
       </c>
       <c r="B27" t="n">
-        <v>58637</v>
+        <v>58443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R27" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,7 +3498,7 @@
         <v>133034592</v>
       </c>
       <c r="B28" t="n">
-        <v>58498</v>
+        <v>58501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>133034492</v>
       </c>
       <c r="B29" t="n">
-        <v>58637</v>
+        <v>58640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B30" t="n">
-        <v>58328</v>
+        <v>58443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B31" t="n">
-        <v>58440</v>
+        <v>58331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3918,7 +3918,7 @@
         <v>133034573</v>
       </c>
       <c r="B32" t="n">
-        <v>58113</v>
+        <v>58116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2865,32 +2865,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133035510</v>
+        <v>133035527</v>
       </c>
       <c r="B22" t="n">
-        <v>58443</v>
+        <v>58501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,32 +2970,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133035527</v>
+        <v>133035510</v>
       </c>
       <c r="B23" t="n">
-        <v>58501</v>
+        <v>58443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3285,32 +3285,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133036146</v>
+        <v>133035361</v>
       </c>
       <c r="B26" t="n">
-        <v>58640</v>
+        <v>58443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R26" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,32 +3390,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133035361</v>
+        <v>133036146</v>
       </c>
       <c r="B27" t="n">
-        <v>58443</v>
+        <v>58640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R27" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B30" t="n">
-        <v>58443</v>
+        <v>58331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B31" t="n">
-        <v>58331</v>
+        <v>58443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B30" t="n">
-        <v>58331</v>
+        <v>58443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B31" t="n">
-        <v>58443</v>
+        <v>58331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4018,6 +4018,111 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133357958</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58443</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>567571</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6509593</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B30" t="n">
-        <v>58443</v>
+        <v>58331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B31" t="n">
-        <v>58331</v>
+        <v>58443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -2329,7 +2329,7 @@
         <v>132455583</v>
       </c>
       <c r="B17" t="n">
-        <v>58331</v>
+        <v>58332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>132455861</v>
       </c>
       <c r="B18" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>132863077</v>
       </c>
       <c r="B19" t="n">
-        <v>58606</v>
+        <v>58607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>132863110</v>
       </c>
       <c r="B20" t="n">
-        <v>58331</v>
+        <v>58332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>132863104</v>
       </c>
       <c r="B21" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>133035527</v>
       </c>
       <c r="B22" t="n">
-        <v>58501</v>
+        <v>58502</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>133035510</v>
       </c>
       <c r="B23" t="n">
-        <v>58443</v>
+        <v>58444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>133036139</v>
       </c>
       <c r="B24" t="n">
-        <v>58331</v>
+        <v>58332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>133034484</v>
       </c>
       <c r="B25" t="n">
-        <v>58443</v>
+        <v>58444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>133035361</v>
       </c>
       <c r="B26" t="n">
-        <v>58443</v>
+        <v>58444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>133036146</v>
       </c>
       <c r="B27" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133034592</v>
       </c>
       <c r="B28" t="n">
-        <v>58501</v>
+        <v>58502</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>133034492</v>
       </c>
       <c r="B29" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034467</v>
+        <v>133034323</v>
       </c>
       <c r="B30" t="n">
-        <v>58331</v>
+        <v>58444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034323</v>
+        <v>133034467</v>
       </c>
       <c r="B31" t="n">
-        <v>58443</v>
+        <v>58332</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3918,7 +3918,7 @@
         <v>133034573</v>
       </c>
       <c r="B32" t="n">
-        <v>58116</v>
+        <v>58117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>133357958</v>
       </c>
       <c r="B33" t="n">
-        <v>58443</v>
+        <v>58444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123307520</v>
+        <v>129403649</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567527</v>
+        <v>567445</v>
       </c>
       <c r="R2" t="n">
-        <v>6509582</v>
+        <v>6509539</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,46 +784,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127679939</v>
+        <v>131861026</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567571</v>
+        <v>567581</v>
       </c>
       <c r="R3" t="n">
-        <v>6509585</v>
+        <v>6509590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,69 +885,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128725191</v>
+        <v>131861113</v>
       </c>
       <c r="B4" t="n">
-        <v>56652</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567548</v>
+        <v>567419</v>
       </c>
       <c r="R4" t="n">
-        <v>6509541</v>
+        <v>6509482</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,7 +989,7 @@
         <v>129403662</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129403649</v>
+        <v>131257158</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,34 +1106,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567445</v>
+        <v>567581</v>
       </c>
       <c r="R6" t="n">
-        <v>6509539</v>
+        <v>6509575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1182,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131191459</v>
+        <v>131289358</v>
       </c>
       <c r="B7" t="n">
-        <v>58057</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,7 +1233,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1310,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567527</v>
+        <v>567544</v>
       </c>
       <c r="R7" t="n">
-        <v>6509582</v>
+        <v>6509595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,12 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,14 +1305,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257158</v>
+        <v>131527895</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1415,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567581</v>
+        <v>567425</v>
       </c>
       <c r="R8" t="n">
-        <v>6509575</v>
+        <v>6509535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,12 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,14 +1410,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131527895</v>
+        <v>131713039</v>
       </c>
       <c r="B9" t="n">
-        <v>57911</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1505,12 +1438,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1520,13 +1461,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567425</v>
+        <v>567414</v>
       </c>
       <c r="R9" t="n">
-        <v>6509535</v>
+        <v>6509506</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,12 +1491,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,32 +1528,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131713039</v>
+        <v>134250580</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>57776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102118</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1616,14 +1562,10 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1663,17 +1605,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,27 +1647,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131765843</v>
+        <v>132333380</v>
       </c>
       <c r="B11" t="n">
-        <v>58597</v>
+        <v>58519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1728,18 +1675,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1747,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R11" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1777,12 +1716,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131861026</v>
+        <v>133034592</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>58519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,26 +1759,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,13 +1791,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567581</v>
+        <v>567414</v>
       </c>
       <c r="R12" t="n">
-        <v>6509590</v>
+        <v>6509506</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,12 +1821,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,7 +1835,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1910,27 +1853,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131861151</v>
+        <v>133035527</v>
       </c>
       <c r="B13" t="n">
-        <v>58597</v>
+        <v>58519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1953,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R13" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1983,12 +1926,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132110067</v>
+        <v>132455583</v>
       </c>
       <c r="B14" t="n">
-        <v>58637</v>
+        <v>58349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,16 +1969,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2043,7 +1986,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
@@ -2054,17 +2001,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567468</v>
+        <v>567548</v>
       </c>
       <c r="R14" t="n">
-        <v>6509548</v>
+        <v>6509541</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,12 +2035,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132110198</v>
+        <v>132863110</v>
       </c>
       <c r="B15" t="n">
-        <v>58637</v>
+        <v>58349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,16 +2088,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2163,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567553</v>
+        <v>567541</v>
       </c>
       <c r="R15" t="n">
-        <v>6509570</v>
+        <v>6509560</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,12 +2150,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132333380</v>
+        <v>133034467</v>
       </c>
       <c r="B16" t="n">
-        <v>58501</v>
+        <v>58349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,16 +2193,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2256,7 +2213,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R16" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2294,12 +2255,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132455583</v>
+        <v>133035486</v>
       </c>
       <c r="B17" t="n">
-        <v>58332</v>
+        <v>58349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,11 +2315,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
@@ -2369,17 +2326,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R17" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,22 +2360,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132455861</v>
+        <v>133833753</v>
       </c>
       <c r="B18" t="n">
-        <v>58641</v>
+        <v>58349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,16 +2403,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2484,14 +2431,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567548</v>
+        <v>567571</v>
       </c>
       <c r="R18" t="n">
-        <v>6509541</v>
+        <v>6509593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2518,12 +2465,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,40 +2497,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132863077</v>
+        <v>132863200</v>
       </c>
       <c r="B19" t="n">
-        <v>58607</v>
+        <v>58461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2655,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132863110</v>
+        <v>133034484</v>
       </c>
       <c r="B20" t="n">
-        <v>58332</v>
+        <v>58461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567541</v>
+        <v>567414</v>
       </c>
       <c r="R20" t="n">
-        <v>6509560</v>
+        <v>6509506</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2728,12 +2679,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132863104</v>
+        <v>133034912</v>
       </c>
       <c r="B21" t="n">
-        <v>58641</v>
+        <v>58461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2803,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R21" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2833,12 +2784,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,10 +2816,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133035527</v>
+        <v>133035510</v>
       </c>
       <c r="B22" t="n">
-        <v>58502</v>
+        <v>58461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2827,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,14 +2921,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133035510</v>
+        <v>133357958</v>
       </c>
       <c r="B23" t="n">
-        <v>58444</v>
+        <v>58461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3013,13 +2964,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567542</v>
+        <v>567571</v>
       </c>
       <c r="R23" t="n">
-        <v>6509592</v>
+        <v>6509593</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3043,12 +2994,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,27 +3026,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133036139</v>
+        <v>133034573</v>
       </c>
       <c r="B24" t="n">
-        <v>58332</v>
+        <v>58134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3108,7 +3059,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3118,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R24" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3148,12 +3099,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133034484</v>
+        <v>131191459</v>
       </c>
       <c r="B25" t="n">
-        <v>58444</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,7 +3164,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3223,13 +3174,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567414</v>
+        <v>567527</v>
       </c>
       <c r="R25" t="n">
-        <v>6509506</v>
+        <v>6509582</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,12 +3204,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133036146</v>
+        <v>132455647</v>
       </c>
       <c r="B26" t="n">
-        <v>58641</v>
+        <v>58131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3296,16 +3247,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3313,7 +3264,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
@@ -3324,17 +3279,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567542</v>
+        <v>567548</v>
       </c>
       <c r="R26" t="n">
-        <v>6509592</v>
+        <v>6509541</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3358,12 +3313,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,35 +3355,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133035361</v>
+        <v>131765843</v>
       </c>
       <c r="B27" t="n">
-        <v>58444</v>
+        <v>58624</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
@@ -3433,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R27" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3463,12 +3432,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,27 +3464,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133034592</v>
+        <v>131861151</v>
       </c>
       <c r="B28" t="n">
-        <v>58502</v>
+        <v>58624</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102990</v>
+        <v>103042</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3528,7 +3497,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3538,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R28" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3568,12 +3537,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,27 +3569,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133034492</v>
+        <v>132863077</v>
       </c>
       <c r="B29" t="n">
-        <v>58641</v>
+        <v>58624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3643,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R29" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3673,12 +3642,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,32 +3674,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133034323</v>
+        <v>132110067</v>
       </c>
       <c r="B30" t="n">
-        <v>58444</v>
+        <v>58658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,7 +3707,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3748,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3778,12 +3747,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133034467</v>
+        <v>132110198</v>
       </c>
       <c r="B31" t="n">
-        <v>58332</v>
+        <v>58658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3821,16 +3790,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3853,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567414</v>
+        <v>567553</v>
       </c>
       <c r="R31" t="n">
-        <v>6509506</v>
+        <v>6509570</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3883,12 +3852,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,27 +3884,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133034573</v>
+        <v>132455861</v>
       </c>
       <c r="B32" t="n">
-        <v>58117</v>
+        <v>58658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3948,23 +3917,23 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567414</v>
+        <v>567548</v>
       </c>
       <c r="R32" t="n">
-        <v>6509506</v>
+        <v>6509541</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3988,12 +3957,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4020,32 +3989,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133357958</v>
+        <v>132863104</v>
       </c>
       <c r="B33" t="n">
-        <v>58461</v>
+        <v>58658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,13 +4032,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567571</v>
+        <v>567541</v>
       </c>
       <c r="R33" t="n">
-        <v>6509593</v>
+        <v>6509560</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4093,12 +4062,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4125,10 +4094,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133833753</v>
+        <v>133034492</v>
       </c>
       <c r="B34" t="n">
-        <v>58349</v>
+        <v>58658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4136,16 +4105,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4168,13 +4137,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567571</v>
+        <v>567414</v>
       </c>
       <c r="R34" t="n">
-        <v>6509593</v>
+        <v>6509506</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4198,12 +4167,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4230,10 +4199,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134250580</v>
+        <v>133036146</v>
       </c>
       <c r="B35" t="n">
-        <v>57776</v>
+        <v>58658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4241,28 +4210,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102118</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -4277,10 +4242,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567414</v>
+        <v>567542</v>
       </c>
       <c r="R35" t="n">
-        <v>6509506</v>
+        <v>6509592</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4307,22 +4272,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>23:30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,6 +4301,724 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128725191</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>567548</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6509541</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133696004</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134210232</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123307520</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>567527</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6509582</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127679939</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>567571</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6509585</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129866829</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>567588</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6509596</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3355,27 +3355,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131765843</v>
+        <v>134481404</v>
       </c>
       <c r="B27" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3383,16 +3383,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3402,10 +3398,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567553</v>
+        <v>567542</v>
       </c>
       <c r="R27" t="n">
-        <v>6509570</v>
+        <v>6509592</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3432,12 +3428,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131861151</v>
+        <v>131765843</v>
       </c>
       <c r="B28" t="n">
         <v>58624</v>
@@ -3492,7 +3488,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R28" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132863077</v>
+        <v>131861151</v>
       </c>
       <c r="B29" t="n">
         <v>58624</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R29" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,27 +3674,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132110067</v>
+        <v>132863077</v>
       </c>
       <c r="B30" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R30" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,7 +3779,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B31" t="n">
         <v>58658</v>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R31" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,7 +3884,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132455861</v>
+        <v>132110198</v>
       </c>
       <c r="B32" t="n">
         <v>58658</v>
@@ -3923,17 +3923,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567548</v>
+        <v>567553</v>
       </c>
       <c r="R32" t="n">
-        <v>6509541</v>
+        <v>6509570</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,7 +3989,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132863104</v>
+        <v>132455861</v>
       </c>
       <c r="B33" t="n">
         <v>58658</v>
@@ -4028,17 +4028,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R33" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,7 +4094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133034492</v>
+        <v>132863104</v>
       </c>
       <c r="B34" t="n">
         <v>58658</v>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R34" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4199,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133036146</v>
+        <v>133034492</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R35" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,10 +4304,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128725191</v>
+        <v>133036146</v>
       </c>
       <c r="B36" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4315,58 +4315,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R36" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4390,22 +4377,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4414,7 +4391,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4433,10 +4409,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133696004</v>
+        <v>128725191</v>
       </c>
       <c r="B37" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4463,7 +4439,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4475,23 +4451,27 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567573</v>
+        <v>567548</v>
       </c>
       <c r="R37" t="n">
-        <v>6509528</v>
+        <v>6509541</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4515,12 +4495,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4548,10 +4538,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134210232</v>
+        <v>133696004</v>
       </c>
       <c r="B38" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,39 +4549,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4629,12 +4620,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4662,57 +4653,62 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123307520</v>
+        <v>134480243</v>
       </c>
       <c r="B39" t="n">
-        <v>99118</v>
+        <v>56896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>208257</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567527</v>
+        <v>567507</v>
       </c>
       <c r="R39" t="n">
-        <v>6509582</v>
+        <v>6509595</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4739,27 +4735,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4787,37 +4768,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127679939</v>
+        <v>134210232</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4825,19 +4806,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567571</v>
+        <v>567573</v>
       </c>
       <c r="R40" t="n">
-        <v>6509585</v>
+        <v>6509528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4864,22 +4849,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4907,7 +4882,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129866829</v>
+        <v>123307520</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4937,7 +4912,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4945,19 +4920,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567588</v>
+        <v>567527</v>
       </c>
       <c r="R41" t="n">
-        <v>6509596</v>
+        <v>6509582</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4979,42 +4957,284 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y41" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127679939</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>567571</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6509585</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129866829</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>567588</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6509596</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Karin Nyström</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>123307520</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti är det minst 30 st.</t>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5240,6 +5240,108 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B44" t="n">
+        <v>107696</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134250580</v>
+        <v>135517450</v>
       </c>
       <c r="B10" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,33 +1539,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R10" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,38 +1647,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132333380</v>
+        <v>134250580</v>
       </c>
       <c r="B11" t="n">
-        <v>58519</v>
+        <v>57776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>102118</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1686,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R11" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1716,12 +1724,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133034592</v>
+        <v>132333380</v>
       </c>
       <c r="B12" t="n">
         <v>58519</v>
@@ -1779,11 +1797,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R12" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1821,12 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133035527</v>
+        <v>133034592</v>
       </c>
       <c r="B13" t="n">
         <v>58519</v>
@@ -1886,7 +1900,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1896,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R13" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1926,12 +1940,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,27 +1972,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132455583</v>
+        <v>133035527</v>
       </c>
       <c r="B14" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1986,11 +2000,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
@@ -2001,17 +2011,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R14" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2035,22 +2045,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132863110</v>
+        <v>132455583</v>
       </c>
       <c r="B15" t="n">
         <v>58349</v>
@@ -2105,7 +2105,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -2116,17 +2120,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R15" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,12 +2154,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,7 +2196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133034467</v>
+        <v>132863110</v>
       </c>
       <c r="B16" t="n">
         <v>58349</v>
@@ -2225,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R16" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2255,12 +2269,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,7 +2301,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133035486</v>
+        <v>133034467</v>
       </c>
       <c r="B17" t="n">
         <v>58349</v>
@@ -2330,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R17" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2360,12 +2374,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,7 +2406,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133833753</v>
+        <v>133035486</v>
       </c>
       <c r="B18" t="n">
         <v>58349</v>
@@ -2435,13 +2449,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R18" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2465,12 +2479,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132863200</v>
+        <v>133833753</v>
       </c>
       <c r="B19" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,33 +2522,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2544,13 +2554,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567541</v>
+        <v>567571</v>
       </c>
       <c r="R19" t="n">
-        <v>6509560</v>
+        <v>6509593</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2574,12 +2584,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133034484</v>
+        <v>132863200</v>
       </c>
       <c r="B20" t="n">
         <v>58461</v>
@@ -2634,12 +2644,16 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2649,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R20" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2679,12 +2693,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133034912</v>
+        <v>133034484</v>
       </c>
       <c r="B21" t="n">
         <v>58461</v>
@@ -2754,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R21" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2816,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133035510</v>
+        <v>133034912</v>
       </c>
       <c r="B22" t="n">
         <v>58461</v>
@@ -2859,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R22" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2889,12 +2903,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133357958</v>
+        <v>133035510</v>
       </c>
       <c r="B23" t="n">
         <v>58461</v>
@@ -2964,13 +2978,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R23" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2994,12 +3008,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,32 +3040,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133034573</v>
+        <v>133357958</v>
       </c>
       <c r="B24" t="n">
-        <v>58134</v>
+        <v>58461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,7 +3073,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3069,13 +3083,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567414</v>
+        <v>567571</v>
       </c>
       <c r="R24" t="n">
-        <v>6509506</v>
+        <v>6509593</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,12 +3113,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131191459</v>
+        <v>133034573</v>
       </c>
       <c r="B25" t="n">
-        <v>58114</v>
+        <v>58134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3156,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3174,13 +3188,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567527</v>
+        <v>567414</v>
       </c>
       <c r="R25" t="n">
-        <v>6509582</v>
+        <v>6509506</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3204,12 +3218,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,60 +3250,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132455647</v>
+        <v>131191459</v>
       </c>
       <c r="B26" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567548</v>
+        <v>567527</v>
       </c>
       <c r="R26" t="n">
-        <v>6509541</v>
+        <v>6509582</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3313,22 +3323,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,7 +3355,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134481404</v>
+        <v>132455647</v>
       </c>
       <c r="B27" t="n">
         <v>58131</v>
@@ -3383,28 +3383,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567542</v>
+        <v>567548</v>
       </c>
       <c r="R27" t="n">
-        <v>6509592</v>
+        <v>6509541</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3428,12 +3432,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,27 +3474,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131765843</v>
+        <v>134481404</v>
       </c>
       <c r="B28" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3488,16 +3502,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3507,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567553</v>
+        <v>567542</v>
       </c>
       <c r="R28" t="n">
-        <v>6509570</v>
+        <v>6509592</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3537,12 +3547,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,7 +3579,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131861151</v>
+        <v>131765843</v>
       </c>
       <c r="B29" t="n">
         <v>58624</v>
@@ -3597,7 +3607,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
@@ -3612,10 +3626,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R29" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3642,12 +3656,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132863077</v>
+        <v>131861151</v>
       </c>
       <c r="B30" t="n">
         <v>58624</v>
@@ -3717,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3747,12 +3761,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,27 +3793,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132110067</v>
+        <v>132863077</v>
       </c>
       <c r="B31" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3822,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R31" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3852,12 +3866,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B32" t="n">
         <v>58658</v>
@@ -3927,10 +3941,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R32" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3957,12 +3971,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,7 +4003,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132455861</v>
+        <v>132110198</v>
       </c>
       <c r="B33" t="n">
         <v>58658</v>
@@ -4028,17 +4042,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567548</v>
+        <v>567553</v>
       </c>
       <c r="R33" t="n">
-        <v>6509541</v>
+        <v>6509570</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4062,12 +4076,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,7 +4108,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132863104</v>
+        <v>132455861</v>
       </c>
       <c r="B34" t="n">
         <v>58658</v>
@@ -4133,17 +4147,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R34" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4167,12 +4181,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4213,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133034492</v>
+        <v>132863104</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4242,10 +4256,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R35" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4272,12 +4286,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4304,7 +4318,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036146</v>
+        <v>133034492</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4347,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R36" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4377,12 +4391,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4409,10 +4423,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128725191</v>
+        <v>133036146</v>
       </c>
       <c r="B37" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,58 +4434,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R37" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4495,22 +4496,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,7 +4510,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4538,10 +4528,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133696004</v>
+        <v>128725191</v>
       </c>
       <c r="B38" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,7 +4558,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4580,23 +4570,27 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567573</v>
+        <v>567548</v>
       </c>
       <c r="R38" t="n">
-        <v>6509528</v>
+        <v>6509541</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4620,12 +4614,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,7 +4657,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134480243</v>
+        <v>133696004</v>
       </c>
       <c r="B39" t="n">
         <v>56896</v>
@@ -4683,7 +4687,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -4695,20 +4699,20 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567507</v>
+        <v>567573</v>
       </c>
       <c r="R39" t="n">
-        <v>6509595</v>
+        <v>6509528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,12 +4739,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,10 +4772,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134210232</v>
+        <v>134480243</v>
       </c>
       <c r="B40" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4779,50 +4783,51 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567573</v>
+        <v>567507</v>
       </c>
       <c r="R40" t="n">
-        <v>6509528</v>
+        <v>6509595</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4849,12 +4854,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4882,37 +4887,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307520</v>
+        <v>134210232</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4920,19 +4925,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567527</v>
+        <v>567573</v>
       </c>
       <c r="R41" t="n">
-        <v>6509582</v>
+        <v>6509528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4959,27 +4968,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5007,7 +5001,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127679939</v>
+        <v>123307520</v>
       </c>
       <c r="B42" t="n">
         <v>99195</v>
@@ -5037,7 +5031,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5054,10 +5048,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>567571</v>
+        <v>567527</v>
       </c>
       <c r="R42" t="n">
-        <v>6509585</v>
+        <v>6509582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5100,6 +5094,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5127,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129866829</v>
+        <v>127679939</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5165,19 +5164,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>567588</v>
+        <v>567571</v>
       </c>
       <c r="R43" t="n">
-        <v>6509596</v>
+        <v>6509585</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5199,34 +5201,40 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5234,60 +5242,61 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135331676</v>
+        <v>129866829</v>
       </c>
       <c r="B44" t="n">
-        <v>107696</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224272</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guldgul ängskovall</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. hians</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Druce</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>567573</v>
+        <v>567588</v>
       </c>
       <c r="R44" t="n">
-        <v>6509528</v>
+        <v>6509596</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5309,14 +5318,19 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5325,14 +5339,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5340,7 +5353,113 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B45" t="n">
+        <v>107696</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131861026</v>
+        <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,37 +795,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567581</v>
+        <v>567419</v>
       </c>
       <c r="R3" t="n">
-        <v>6509590</v>
+        <v>6509482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131861113</v>
+        <v>131861026</v>
       </c>
       <c r="B4" t="n">
         <v>91995</v>
@@ -919,14 +927,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567419</v>
+        <v>567581</v>
       </c>
       <c r="R4" t="n">
-        <v>6509482</v>
+        <v>6509590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403662</v>
+        <v>131861113</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,45 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567445</v>
+        <v>567419</v>
       </c>
       <c r="R5" t="n">
-        <v>6509539</v>
+        <v>6509482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,42 +1095,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257158</v>
+        <v>129403662</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567581</v>
+        <v>567445</v>
       </c>
       <c r="R6" t="n">
-        <v>6509575</v>
+        <v>6509539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,6 +1185,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131289358</v>
+        <v>131257158</v>
       </c>
       <c r="B7" t="n">
         <v>57950</v>
@@ -1243,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567544</v>
+        <v>567581</v>
       </c>
       <c r="R7" t="n">
-        <v>6509595</v>
+        <v>6509575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,12 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,7 +1309,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131527895</v>
+        <v>131289358</v>
       </c>
       <c r="B8" t="n">
         <v>57950</v>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567425</v>
+        <v>567544</v>
       </c>
       <c r="R8" t="n">
-        <v>6509535</v>
+        <v>6509595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131713039</v>
+        <v>131527895</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,20 +1442,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1461,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567414</v>
+        <v>567425</v>
       </c>
       <c r="R9" t="n">
-        <v>6509506</v>
+        <v>6509535</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,17 +1487,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,7 +1519,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135517450</v>
+        <v>131713039</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1558,11 +1549,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -1575,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R10" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1605,22 +1600,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134250580</v>
+        <v>135517450</v>
       </c>
       <c r="B11" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,33 +1648,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1694,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R11" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1724,22 +1714,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,38 +1756,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132333380</v>
+        <v>134250580</v>
       </c>
       <c r="B12" t="n">
-        <v>58519</v>
+        <v>57776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>102118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1805,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R12" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1835,12 +1833,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1875,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133034592</v>
+        <v>132333380</v>
       </c>
       <c r="B13" t="n">
         <v>58519</v>
@@ -1898,11 +1906,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R13" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1940,12 +1944,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1976,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133035527</v>
+        <v>133034592</v>
       </c>
       <c r="B14" t="n">
         <v>58519</v>
@@ -2005,7 +2009,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2015,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R14" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2045,12 +2049,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,27 +2081,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132455583</v>
+        <v>133035527</v>
       </c>
       <c r="B15" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2105,11 +2109,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -2120,17 +2120,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R15" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2154,22 +2154,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132863110</v>
+        <v>132455583</v>
       </c>
       <c r="B16" t="n">
         <v>58349</v>
@@ -2224,7 +2214,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2235,17 +2229,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R16" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2269,12 +2263,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133034467</v>
+        <v>132863110</v>
       </c>
       <c r="B17" t="n">
         <v>58349</v>
@@ -2344,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R17" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2374,12 +2378,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,7 +2410,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133035486</v>
+        <v>133034467</v>
       </c>
       <c r="B18" t="n">
         <v>58349</v>
@@ -2449,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R18" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2479,12 +2483,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,7 +2515,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133833753</v>
+        <v>133035486</v>
       </c>
       <c r="B19" t="n">
         <v>58349</v>
@@ -2554,13 +2558,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R19" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,12 +2588,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132863200</v>
+        <v>133833753</v>
       </c>
       <c r="B20" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,33 +2631,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567541</v>
+        <v>567571</v>
       </c>
       <c r="R20" t="n">
-        <v>6509560</v>
+        <v>6509593</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2693,12 +2693,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,7 +2725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133034484</v>
+        <v>132863200</v>
       </c>
       <c r="B21" t="n">
         <v>58461</v>
@@ -2753,12 +2753,16 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2768,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R21" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2798,12 +2802,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2834,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133034912</v>
+        <v>133034484</v>
       </c>
       <c r="B22" t="n">
         <v>58461</v>
@@ -2873,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R22" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2935,7 +2939,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133035510</v>
+        <v>133034912</v>
       </c>
       <c r="B23" t="n">
         <v>58461</v>
@@ -2978,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R23" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3008,12 +3012,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133357958</v>
+        <v>133035510</v>
       </c>
       <c r="B24" t="n">
         <v>58461</v>
@@ -3083,13 +3087,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R24" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3113,12 +3117,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3145,32 +3149,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133034573</v>
+        <v>133357958</v>
       </c>
       <c r="B25" t="n">
-        <v>58134</v>
+        <v>58461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,7 +3182,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3188,13 +3192,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567414</v>
+        <v>567571</v>
       </c>
       <c r="R25" t="n">
-        <v>6509506</v>
+        <v>6509593</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3218,12 +3222,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131191459</v>
+        <v>133034573</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>58134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3261,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,13 +3297,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567527</v>
+        <v>567414</v>
       </c>
       <c r="R26" t="n">
-        <v>6509582</v>
+        <v>6509506</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3323,12 +3327,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,60 +3359,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132455647</v>
+        <v>131191459</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567548</v>
+        <v>567527</v>
       </c>
       <c r="R27" t="n">
-        <v>6509541</v>
+        <v>6509582</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3432,22 +3432,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,7 +3464,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134481404</v>
+        <v>132455647</v>
       </c>
       <c r="B28" t="n">
         <v>58131</v>
@@ -3502,28 +3492,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567542</v>
+        <v>567548</v>
       </c>
       <c r="R28" t="n">
-        <v>6509592</v>
+        <v>6509541</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3547,12 +3541,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,27 +3583,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131765843</v>
+        <v>134481404</v>
       </c>
       <c r="B29" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3607,16 +3611,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567553</v>
+        <v>567542</v>
       </c>
       <c r="R29" t="n">
-        <v>6509570</v>
+        <v>6509592</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131861151</v>
+        <v>131765843</v>
       </c>
       <c r="B30" t="n">
         <v>58624</v>
@@ -3716,7 +3716,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
@@ -3731,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R30" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3761,12 +3765,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3793,7 +3797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132863077</v>
+        <v>131861151</v>
       </c>
       <c r="B31" t="n">
         <v>58624</v>
@@ -3836,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R31" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3866,12 +3870,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,27 +3902,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132110067</v>
+        <v>132863077</v>
       </c>
       <c r="B32" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3941,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R32" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3971,12 +3975,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4003,7 +4007,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B33" t="n">
         <v>58658</v>
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R33" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4076,12 +4080,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4108,7 +4112,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132455861</v>
+        <v>132110198</v>
       </c>
       <c r="B34" t="n">
         <v>58658</v>
@@ -4147,17 +4151,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567548</v>
+        <v>567553</v>
       </c>
       <c r="R34" t="n">
-        <v>6509541</v>
+        <v>6509570</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4181,12 +4185,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,7 +4217,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132863104</v>
+        <v>132455861</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4252,17 +4256,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R35" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4286,12 +4290,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,7 +4322,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133034492</v>
+        <v>132863104</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4361,10 +4365,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R36" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4391,12 +4395,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4427,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133036146</v>
+        <v>133034492</v>
       </c>
       <c r="B37" t="n">
         <v>58658</v>
@@ -4466,10 +4470,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R37" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4496,12 +4500,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4528,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128725191</v>
+        <v>133036146</v>
       </c>
       <c r="B38" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4539,58 +4543,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R38" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4614,22 +4605,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4638,7 +4619,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4657,10 +4637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133696004</v>
+        <v>128725191</v>
       </c>
       <c r="B39" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4687,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -4699,23 +4679,27 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567573</v>
+        <v>567548</v>
       </c>
       <c r="R39" t="n">
-        <v>6509528</v>
+        <v>6509541</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4739,12 +4723,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4772,7 +4766,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134480243</v>
+        <v>133696004</v>
       </c>
       <c r="B40" t="n">
         <v>56896</v>
@@ -4802,7 +4796,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -4814,20 +4808,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567507</v>
+        <v>567573</v>
       </c>
       <c r="R40" t="n">
-        <v>6509595</v>
+        <v>6509528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4854,12 +4848,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4887,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134210232</v>
+        <v>134480243</v>
       </c>
       <c r="B41" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4898,50 +4892,51 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567573</v>
+        <v>567507</v>
       </c>
       <c r="R41" t="n">
-        <v>6509528</v>
+        <v>6509595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4968,12 +4963,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5001,37 +4996,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307520</v>
+        <v>134210232</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5039,19 +5034,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>567527</v>
+        <v>567573</v>
       </c>
       <c r="R42" t="n">
-        <v>6509582</v>
+        <v>6509528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5078,27 +5077,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,7 +5110,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127679939</v>
+        <v>123307520</v>
       </c>
       <c r="B43" t="n">
         <v>99195</v>
@@ -5156,7 +5140,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5173,10 +5157,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>567571</v>
+        <v>567527</v>
       </c>
       <c r="R43" t="n">
-        <v>6509585</v>
+        <v>6509582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5219,6 +5203,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129866829</v>
+        <v>127679939</v>
       </c>
       <c r="B44" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5284,19 +5273,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>567588</v>
+        <v>567571</v>
       </c>
       <c r="R44" t="n">
-        <v>6509596</v>
+        <v>6509585</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5318,34 +5310,40 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5353,60 +5351,61 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135331676</v>
+        <v>129866829</v>
       </c>
       <c r="B45" t="n">
-        <v>107696</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224272</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guldgul ängskovall</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. hians</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Druce</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>567573</v>
+        <v>567588</v>
       </c>
       <c r="R45" t="n">
-        <v>6509528</v>
+        <v>6509596</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5428,14 +5427,19 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,14 +5448,13 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5459,7 +5462,113 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107696</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129403649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135531478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131861026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131861113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129403662</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131257158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131289358</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131527895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131713039</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135517450</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134250580</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132333380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034592</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133035527</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132455583</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2407,6 +2487,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132863110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,6 +2597,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034467</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2617,6 +2707,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133035486</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2722,6 +2817,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133833753</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2831,6 +2931,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132863200</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2936,6 +3041,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3041,6 +3151,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034912</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133035510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3251,6 +3371,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133357958</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3356,6 +3481,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034573</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3461,6 +3591,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191459</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3580,6 +3715,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132455647</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3685,6 +3825,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134481404</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3794,6 +3939,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131765843</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3899,6 +4049,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131861151</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4004,6 +4159,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132863077</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4109,6 +4269,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132110067</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4214,6 +4379,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132110198</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4319,6 +4489,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132455861</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4424,6 +4599,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132863104</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4529,6 +4709,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133034492</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4634,6 +4819,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036146</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4763,6 +4953,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128725191</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4878,6 +5073,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696004</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4993,6 +5193,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134480243</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5107,6 +5312,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134210232</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5232,6 +5442,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307520</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5352,6 +5567,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127679939</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5465,6 +5685,11 @@
       <c r="AY45" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866829</t>
         </is>
       </c>
     </row>
@@ -5569,8 +5794,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>135517450</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>135331676</v>
       </c>
       <c r="B46" t="n">
-        <v>107696</v>
+        <v>107751</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>135331676</v>
       </c>
       <c r="B46" t="n">
-        <v>107751</v>
+        <v>107778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131861026</v>
+        <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>93345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,37 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567581</v>
+        <v>567419</v>
       </c>
       <c r="R3" t="n">
-        <v>6509590</v>
+        <v>6509482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,13 +902,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861026</t>
+          <t>https://artportalen.se/Sighting/135531478</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131861113</v>
+        <v>131861026</v>
       </c>
       <c r="B4" t="n">
         <v>91995</v>
@@ -934,14 +942,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567419</v>
+        <v>567581</v>
       </c>
       <c r="R4" t="n">
-        <v>6509482</v>
+        <v>6509590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,16 +1008,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861113</t>
+          <t>https://artportalen.se/Sighting/131861026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129403662</v>
+        <v>131861113</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,45 +1025,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567445</v>
+        <v>567419</v>
       </c>
       <c r="R5" t="n">
-        <v>6509539</v>
+        <v>6509482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,48 +1114,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129403662</t>
+          <t>https://artportalen.se/Sighting/131861113</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257158</v>
+        <v>129403662</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567581</v>
+        <v>567445</v>
       </c>
       <c r="R6" t="n">
-        <v>6509575</v>
+        <v>6509539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,6 +1210,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,13 +1228,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131257158</t>
+          <t>https://artportalen.se/Sighting/129403662</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131289358</v>
+        <v>131257158</v>
       </c>
       <c r="B7" t="n">
         <v>57950</v>
@@ -1273,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567544</v>
+        <v>567581</v>
       </c>
       <c r="R7" t="n">
-        <v>6509595</v>
+        <v>6509575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,12 +1307,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,13 +1338,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131289358</t>
+          <t>https://artportalen.se/Sighting/131257158</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131527895</v>
+        <v>131289358</v>
       </c>
       <c r="B8" t="n">
         <v>57950</v>
@@ -1383,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567425</v>
+        <v>567544</v>
       </c>
       <c r="R8" t="n">
-        <v>6509535</v>
+        <v>6509595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,12 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,16 +1448,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131527895</t>
+          <t>https://artportalen.se/Sighting/131289358</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131713039</v>
+        <v>131527895</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,20 +1482,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1501,13 +1497,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567414</v>
+        <v>567425</v>
       </c>
       <c r="R9" t="n">
-        <v>6509506</v>
+        <v>6509535</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,17 +1527,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,16 +1558,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131713039</t>
+          <t>https://artportalen.se/Sighting/131527895</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134250580</v>
+        <v>131713039</v>
       </c>
       <c r="B10" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1598,14 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1650,22 +1645,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>23:20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>23:30</t>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ivrigt revirhävdande sedan drygt en vecka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,33 +1681,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134250580</t>
+          <t>https://artportalen.se/Sighting/131713039</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132333380</v>
+        <v>135517450</v>
       </c>
       <c r="B11" t="n">
-        <v>58519</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,10 +1715,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1766,12 +1764,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,46 +1805,50 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132333380</t>
+          <t>https://artportalen.se/Sighting/135517450</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133034592</v>
+        <v>134250580</v>
       </c>
       <c r="B12" t="n">
-        <v>58519</v>
+        <v>57776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>102118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1876,12 +1888,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,13 +1929,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034592</t>
+          <t>https://artportalen.se/Sighting/134250580</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133035527</v>
+        <v>132333380</v>
       </c>
       <c r="B13" t="n">
         <v>58519</v>
@@ -1944,11 +1966,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1956,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R13" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1986,12 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,33 +2035,33 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035527</t>
+          <t>https://artportalen.se/Sighting/132333380</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132455583</v>
+        <v>133034592</v>
       </c>
       <c r="B14" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2051,32 +2069,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567548</v>
+        <v>567414</v>
       </c>
       <c r="R14" t="n">
-        <v>6509541</v>
+        <v>6509506</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,22 +2114,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,33 +2145,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455583</t>
+          <t>https://artportalen.se/Sighting/133034592</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132863110</v>
+        <v>133035527</v>
       </c>
       <c r="B15" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2190,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567541</v>
+        <v>567542</v>
       </c>
       <c r="R15" t="n">
-        <v>6509560</v>
+        <v>6509592</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2220,12 +2224,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,13 +2255,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863110</t>
+          <t>https://artportalen.se/Sighting/133035527</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133034467</v>
+        <v>132455583</v>
       </c>
       <c r="B16" t="n">
         <v>58349</v>
@@ -2285,7 +2289,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2296,17 +2304,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567414</v>
+        <v>567548</v>
       </c>
       <c r="R16" t="n">
-        <v>6509506</v>
+        <v>6509541</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,12 +2338,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,13 +2379,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034467</t>
+          <t>https://artportalen.se/Sighting/132455583</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133035486</v>
+        <v>132863110</v>
       </c>
       <c r="B17" t="n">
         <v>58349</v>
@@ -2410,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567542</v>
+        <v>567541</v>
       </c>
       <c r="R17" t="n">
-        <v>6509592</v>
+        <v>6509560</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2440,12 +2458,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,13 +2489,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035486</t>
+          <t>https://artportalen.se/Sighting/132863110</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133833753</v>
+        <v>133034467</v>
       </c>
       <c r="B18" t="n">
         <v>58349</v>
@@ -2520,13 +2538,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567571</v>
+        <v>567414</v>
       </c>
       <c r="R18" t="n">
-        <v>6509593</v>
+        <v>6509506</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,12 +2568,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,16 +2599,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133833753</t>
+          <t>https://artportalen.se/Sighting/133034467</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132863200</v>
+        <v>133035486</v>
       </c>
       <c r="B19" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,33 +2616,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2634,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567541</v>
+        <v>567542</v>
       </c>
       <c r="R19" t="n">
-        <v>6509560</v>
+        <v>6509592</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2664,12 +2678,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,16 +2709,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863200</t>
+          <t>https://artportalen.se/Sighting/133035486</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133034484</v>
+        <v>133833753</v>
       </c>
       <c r="B20" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,21 +2726,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,13 +2758,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567414</v>
+        <v>567571</v>
       </c>
       <c r="R20" t="n">
-        <v>6509506</v>
+        <v>6509593</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,12 +2788,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,13 +2819,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034484</t>
+          <t>https://artportalen.se/Sighting/133833753</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133034912</v>
+        <v>132863200</v>
       </c>
       <c r="B21" t="n">
         <v>58461</v>
@@ -2839,12 +2853,16 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2854,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R21" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2884,12 +2902,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,13 +2933,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034912</t>
+          <t>https://artportalen.se/Sighting/132863200</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133035510</v>
+        <v>133034484</v>
       </c>
       <c r="B22" t="n">
         <v>58461</v>
@@ -2964,10 +2982,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R22" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2994,12 +3012,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,13 +3043,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035510</t>
+          <t>https://artportalen.se/Sighting/133034484</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133357958</v>
+        <v>133034912</v>
       </c>
       <c r="B23" t="n">
         <v>58461</v>
@@ -3074,13 +3092,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567571</v>
+        <v>567468</v>
       </c>
       <c r="R23" t="n">
-        <v>6509593</v>
+        <v>6509548</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3104,12 +3122,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,38 +3153,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133357958</t>
+          <t>https://artportalen.se/Sighting/133034912</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133034573</v>
+        <v>133035510</v>
       </c>
       <c r="B24" t="n">
-        <v>58134</v>
+        <v>58461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,7 +3192,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3184,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567414</v>
+        <v>567542</v>
       </c>
       <c r="R24" t="n">
-        <v>6509506</v>
+        <v>6509592</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3214,12 +3232,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,38 +3263,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034573</t>
+          <t>https://artportalen.se/Sighting/133035510</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131191459</v>
+        <v>133357958</v>
       </c>
       <c r="B25" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3284,7 +3302,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3294,13 +3312,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567527</v>
+        <v>567571</v>
       </c>
       <c r="R25" t="n">
-        <v>6509582</v>
+        <v>6509593</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,12 +3342,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,33 +3373,33 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191459</t>
+          <t>https://artportalen.se/Sighting/133357958</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132455647</v>
+        <v>133034573</v>
       </c>
       <c r="B26" t="n">
-        <v>58131</v>
+        <v>58134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103023</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3389,32 +3407,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567548</v>
+        <v>567414</v>
       </c>
       <c r="R26" t="n">
-        <v>6509541</v>
+        <v>6509506</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,22 +3452,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,38 +3483,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455647</t>
+          <t>https://artportalen.se/Sighting/133034573</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134481404</v>
+        <v>131191459</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3518,7 +3522,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3528,13 +3532,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567542</v>
+        <v>567527</v>
       </c>
       <c r="R27" t="n">
-        <v>6509592</v>
+        <v>6509582</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,12 +3562,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3589,33 +3593,33 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134481404</t>
+          <t>https://artportalen.se/Sighting/131191459</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131765843</v>
+        <v>132455647</v>
       </c>
       <c r="B28" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3625,7 +3629,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3638,17 +3642,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567553</v>
+        <v>567548</v>
       </c>
       <c r="R28" t="n">
-        <v>6509570</v>
+        <v>6509541</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,12 +3676,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,33 +3717,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131765843</t>
+          <t>https://artportalen.se/Sighting/132455647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131861151</v>
+        <v>134481404</v>
       </c>
       <c r="B29" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3742,7 +3756,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3752,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567468</v>
+        <v>567542</v>
       </c>
       <c r="R29" t="n">
-        <v>6509548</v>
+        <v>6509592</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3782,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,13 +3827,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861151</t>
+          <t>https://artportalen.se/Sighting/134481404</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132863077</v>
+        <v>131765843</v>
       </c>
       <c r="B30" t="n">
         <v>58624</v>
@@ -3847,7 +3861,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
@@ -3862,10 +3880,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567541</v>
+        <v>567553</v>
       </c>
       <c r="R30" t="n">
-        <v>6509560</v>
+        <v>6509570</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3892,12 +3910,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,33 +3941,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863077</t>
+          <t>https://artportalen.se/Sighting/131765843</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132110067</v>
+        <v>131861151</v>
       </c>
       <c r="B31" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4002,12 +4020,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4033,33 +4051,33 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110067</t>
+          <t>https://artportalen.se/Sighting/131861151</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132110198</v>
+        <v>132863077</v>
       </c>
       <c r="B32" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4082,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567553</v>
+        <v>567541</v>
       </c>
       <c r="R32" t="n">
-        <v>6509570</v>
+        <v>6509560</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4112,12 +4130,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,13 +4161,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110198</t>
+          <t>https://artportalen.se/Sighting/132863077</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132455861</v>
+        <v>132110067</v>
       </c>
       <c r="B33" t="n">
         <v>58658</v>
@@ -4188,17 +4206,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567548</v>
+        <v>567468</v>
       </c>
       <c r="R33" t="n">
-        <v>6509541</v>
+        <v>6509548</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,12 +4240,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4253,13 +4271,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455861</t>
+          <t>https://artportalen.se/Sighting/132110067</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132863104</v>
+        <v>132110198</v>
       </c>
       <c r="B34" t="n">
         <v>58658</v>
@@ -4302,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567541</v>
+        <v>567553</v>
       </c>
       <c r="R34" t="n">
-        <v>6509560</v>
+        <v>6509570</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4332,12 +4350,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,13 +4381,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863104</t>
+          <t>https://artportalen.se/Sighting/132110198</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133034492</v>
+        <v>132455861</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4408,17 +4426,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567414</v>
+        <v>567548</v>
       </c>
       <c r="R35" t="n">
-        <v>6509506</v>
+        <v>6509541</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,12 +4460,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,13 +4491,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034492</t>
+          <t>https://artportalen.se/Sighting/132455861</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036146</v>
+        <v>132863104</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4522,10 +4540,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567542</v>
+        <v>567541</v>
       </c>
       <c r="R36" t="n">
-        <v>6509592</v>
+        <v>6509560</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4552,12 +4570,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,16 +4601,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133036146</t>
+          <t>https://artportalen.se/Sighting/132863104</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128725191</v>
+        <v>133034492</v>
       </c>
       <c r="B37" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,58 +4618,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567548</v>
+        <v>567414</v>
       </c>
       <c r="R37" t="n">
-        <v>6509541</v>
+        <v>6509506</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4675,22 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,7 +4694,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4717,16 +4711,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128725191</t>
+          <t>https://artportalen.se/Sighting/133034492</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133696004</v>
+        <v>133036146</v>
       </c>
       <c r="B38" t="n">
-        <v>56896</v>
+        <v>58658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,54 +4728,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567573</v>
+        <v>567542</v>
       </c>
       <c r="R38" t="n">
-        <v>6509528</v>
+        <v>6509592</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4805,12 +4790,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,7 +4804,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4837,16 +4821,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696004</t>
+          <t>https://artportalen.se/Sighting/133036146</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134480243</v>
+        <v>128725191</v>
       </c>
       <c r="B39" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,20 +4872,24 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567507</v>
+        <v>567548</v>
       </c>
       <c r="R39" t="n">
-        <v>6509595</v>
+        <v>6509541</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4925,12 +4913,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,16 +4955,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134480243</t>
+          <t>https://artportalen.se/Sighting/128725191</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134210232</v>
+        <v>133696004</v>
       </c>
       <c r="B40" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4974,39 +4972,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5044,12 +5043,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,63 +5075,68 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134210232</t>
+          <t>https://artportalen.se/Sighting/133696004</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307520</v>
+        <v>134480243</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>56896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>208257</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567527</v>
+        <v>567507</v>
       </c>
       <c r="R41" t="n">
-        <v>6509582</v>
+        <v>6509595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5159,27 +5163,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5206,43 +5195,43 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123307520</t>
+          <t>https://artportalen.se/Sighting/134480243</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127679939</v>
+        <v>134210232</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5250,19 +5239,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>567571</v>
+        <v>567573</v>
       </c>
       <c r="R42" t="n">
-        <v>6509585</v>
+        <v>6509528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,22 +5282,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5331,16 +5314,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127679939</t>
+          <t>https://artportalen.se/Sighting/134210232</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129866829</v>
+        <v>123307520</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5367,7 +5350,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5375,19 +5358,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>567588</v>
+        <v>567527</v>
       </c>
       <c r="R43" t="n">
-        <v>6509596</v>
+        <v>6509582</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5409,34 +5395,45 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5444,62 +5441,66 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129866829</t>
+          <t>https://artportalen.se/Sighting/123307520</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135331676</v>
+        <v>127679939</v>
       </c>
       <c r="B44" t="n">
-        <v>107778</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224272</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guldgul ängskovall</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. hians</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Druce</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>567573</v>
+        <v>567571</v>
       </c>
       <c r="R44" t="n">
-        <v>6509528</v>
+        <v>6509585</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5526,12 +5527,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5557,6 +5568,233 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127679939</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129866829</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sjöberga 1:2, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>567588</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6509596</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866829</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107783</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135331676</t>
         </is>
@@ -5607,6 +5845,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>135331676</v>
       </c>
       <c r="B46" t="n">
-        <v>107783</v>
+        <v>107785</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>135517450</v>
       </c>
       <c r="B11" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135531478</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134250580</v>
+        <v>136274293</v>
       </c>
       <c r="B12" t="n">
-        <v>57776</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,33 +1822,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1858,13 +1854,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567414</v>
+        <v>567489</v>
       </c>
       <c r="R12" t="n">
-        <v>6509506</v>
+        <v>6509582</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,22 +1884,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,44 +1925,52 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134250580</t>
+          <t>https://artportalen.se/Sighting/136274293</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132333380</v>
+        <v>134250580</v>
       </c>
       <c r="B13" t="n">
-        <v>58519</v>
+        <v>57776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>102118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1974,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R13" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2004,12 +2008,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,13 +2049,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132333380</t>
+          <t>https://artportalen.se/Sighting/134250580</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133034592</v>
+        <v>132333380</v>
       </c>
       <c r="B14" t="n">
         <v>58519</v>
@@ -2072,11 +2086,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2084,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567414</v>
+        <v>567468</v>
       </c>
       <c r="R14" t="n">
-        <v>6509506</v>
+        <v>6509548</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2114,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,13 +2155,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034592</t>
+          <t>https://artportalen.se/Sighting/132333380</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133035527</v>
+        <v>133034592</v>
       </c>
       <c r="B15" t="n">
         <v>58519</v>
@@ -2184,7 +2194,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2194,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R15" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2224,12 +2234,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,33 +2265,33 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035527</t>
+          <t>https://artportalen.se/Sighting/133034592</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132455583</v>
+        <v>133035527</v>
       </c>
       <c r="B16" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2289,11 +2299,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -2304,17 +2310,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R16" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,22 +2344,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,13 +2375,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455583</t>
+          <t>https://artportalen.se/Sighting/133035527</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132863110</v>
+        <v>132455583</v>
       </c>
       <c r="B17" t="n">
         <v>58349</v>
@@ -2413,7 +2409,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
@@ -2424,17 +2424,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R17" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,12 +2458,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,13 +2499,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863110</t>
+          <t>https://artportalen.se/Sighting/132455583</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133034467</v>
+        <v>132863110</v>
       </c>
       <c r="B18" t="n">
         <v>58349</v>
@@ -2538,10 +2548,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R18" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2568,12 +2578,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,13 +2609,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034467</t>
+          <t>https://artportalen.se/Sighting/132863110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133035486</v>
+        <v>133034467</v>
       </c>
       <c r="B19" t="n">
         <v>58349</v>
@@ -2648,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R19" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2678,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,13 +2719,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035486</t>
+          <t>https://artportalen.se/Sighting/133034467</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133833753</v>
+        <v>133035486</v>
       </c>
       <c r="B20" t="n">
         <v>58349</v>
@@ -2758,13 +2768,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R20" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2788,12 +2798,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,16 +2829,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133833753</t>
+          <t>https://artportalen.se/Sighting/133035486</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132863200</v>
+        <v>133833753</v>
       </c>
       <c r="B21" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,33 +2846,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2872,13 +2878,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567541</v>
+        <v>567571</v>
       </c>
       <c r="R21" t="n">
-        <v>6509560</v>
+        <v>6509593</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,12 +2908,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,13 +2939,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863200</t>
+          <t>https://artportalen.se/Sighting/133833753</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133034484</v>
+        <v>132863200</v>
       </c>
       <c r="B22" t="n">
         <v>58461</v>
@@ -2967,12 +2973,16 @@
           <t>(Pallas, 1764)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2982,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R22" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3012,12 +3022,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,13 +3053,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034484</t>
+          <t>https://artportalen.se/Sighting/132863200</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133034912</v>
+        <v>133034484</v>
       </c>
       <c r="B23" t="n">
         <v>58461</v>
@@ -3092,10 +3102,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567468</v>
+        <v>567414</v>
       </c>
       <c r="R23" t="n">
-        <v>6509548</v>
+        <v>6509506</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3153,13 +3163,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034912</t>
+          <t>https://artportalen.se/Sighting/133034484</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133035510</v>
+        <v>133034912</v>
       </c>
       <c r="B24" t="n">
         <v>58461</v>
@@ -3202,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567542</v>
+        <v>567468</v>
       </c>
       <c r="R24" t="n">
-        <v>6509592</v>
+        <v>6509548</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3232,12 +3242,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,13 +3273,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133035510</t>
+          <t>https://artportalen.se/Sighting/133034912</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133357958</v>
+        <v>133035510</v>
       </c>
       <c r="B25" t="n">
         <v>58461</v>
@@ -3312,13 +3322,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567571</v>
+        <v>567542</v>
       </c>
       <c r="R25" t="n">
-        <v>6509593</v>
+        <v>6509592</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,12 +3352,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,38 +3383,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133357958</t>
+          <t>https://artportalen.se/Sighting/133035510</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133034573</v>
+        <v>133357958</v>
       </c>
       <c r="B26" t="n">
-        <v>58134</v>
+        <v>58461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,7 +3422,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3422,13 +3432,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567414</v>
+        <v>567571</v>
       </c>
       <c r="R26" t="n">
-        <v>6509506</v>
+        <v>6509593</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,12 +3462,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,16 +3493,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034573</t>
+          <t>https://artportalen.se/Sighting/133357958</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131191459</v>
+        <v>133034573</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>58134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,13 +3542,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567527</v>
+        <v>567414</v>
       </c>
       <c r="R27" t="n">
-        <v>6509582</v>
+        <v>6509506</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,12 +3572,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,66 +3603,62 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131191459</t>
+          <t>https://artportalen.se/Sighting/133034573</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132455647</v>
+        <v>131191459</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567548</v>
+        <v>567527</v>
       </c>
       <c r="R28" t="n">
-        <v>6509541</v>
+        <v>6509582</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3676,22 +3682,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,13 +3713,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455647</t>
+          <t>https://artportalen.se/Sighting/131191459</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134481404</v>
+        <v>132455647</v>
       </c>
       <c r="B29" t="n">
         <v>58131</v>
@@ -3751,28 +3747,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567542</v>
+        <v>567548</v>
       </c>
       <c r="R29" t="n">
-        <v>6509592</v>
+        <v>6509541</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3796,12 +3796,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,33 +3837,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134481404</t>
+          <t>https://artportalen.se/Sighting/132455647</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131765843</v>
+        <v>134481404</v>
       </c>
       <c r="B30" t="n">
-        <v>58624</v>
+        <v>58131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3861,16 +3871,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3880,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567553</v>
+        <v>567542</v>
       </c>
       <c r="R30" t="n">
-        <v>6509570</v>
+        <v>6509592</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3910,12 +3916,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,13 +3947,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131765843</t>
+          <t>https://artportalen.se/Sighting/134481404</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131861151</v>
+        <v>131765843</v>
       </c>
       <c r="B31" t="n">
         <v>58624</v>
@@ -3975,7 +3981,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
@@ -3990,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R31" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4020,12 +4030,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,13 +4061,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861151</t>
+          <t>https://artportalen.se/Sighting/131765843</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132863077</v>
+        <v>131861151</v>
       </c>
       <c r="B32" t="n">
         <v>58624</v>
@@ -4100,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R32" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4130,12 +4140,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,33 +4171,33 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863077</t>
+          <t>https://artportalen.se/Sighting/131861151</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132110067</v>
+        <v>132863077</v>
       </c>
       <c r="B33" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4210,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R33" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4240,12 +4250,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,13 +4281,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110067</t>
+          <t>https://artportalen.se/Sighting/132863077</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B34" t="n">
         <v>58658</v>
@@ -4320,10 +4330,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R34" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4350,12 +4360,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,13 +4391,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110198</t>
+          <t>https://artportalen.se/Sighting/132110067</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132455861</v>
+        <v>132110198</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4426,17 +4436,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567548</v>
+        <v>567553</v>
       </c>
       <c r="R35" t="n">
-        <v>6509541</v>
+        <v>6509570</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4460,12 +4470,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,13 +4501,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455861</t>
+          <t>https://artportalen.se/Sighting/132110198</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132863104</v>
+        <v>132455861</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4536,17 +4546,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R36" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,12 +4580,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4601,13 +4611,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863104</t>
+          <t>https://artportalen.se/Sighting/132455861</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133034492</v>
+        <v>132863104</v>
       </c>
       <c r="B37" t="n">
         <v>58658</v>
@@ -4650,10 +4660,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R37" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4680,12 +4690,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,13 +4721,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034492</t>
+          <t>https://artportalen.se/Sighting/132863104</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133036146</v>
+        <v>133034492</v>
       </c>
       <c r="B38" t="n">
         <v>58658</v>
@@ -4760,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R38" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4790,12 +4800,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,16 +4831,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133036146</t>
+          <t>https://artportalen.se/Sighting/133034492</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128725191</v>
+        <v>133036146</v>
       </c>
       <c r="B39" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4838,58 +4848,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R39" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4913,22 +4910,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4937,7 +4924,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4955,16 +4941,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128725191</t>
+          <t>https://artportalen.se/Sighting/133036146</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133696004</v>
+        <v>128725191</v>
       </c>
       <c r="B40" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4991,7 +4977,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5003,23 +4989,27 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567573</v>
+        <v>567548</v>
       </c>
       <c r="R40" t="n">
-        <v>6509528</v>
+        <v>6509541</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5043,12 +5033,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,13 +5075,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696004</t>
+          <t>https://artportalen.se/Sighting/128725191</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134480243</v>
+        <v>133696004</v>
       </c>
       <c r="B41" t="n">
         <v>56896</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5123,20 +5123,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567507</v>
+        <v>567573</v>
       </c>
       <c r="R41" t="n">
-        <v>6509595</v>
+        <v>6509528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,16 +5195,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134480243</t>
+          <t>https://artportalen.se/Sighting/133696004</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134210232</v>
+        <v>134480243</v>
       </c>
       <c r="B42" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,50 +5212,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>567573</v>
+        <v>567507</v>
       </c>
       <c r="R42" t="n">
-        <v>6509528</v>
+        <v>6509595</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5282,12 +5283,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5314,43 +5315,43 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134210232</t>
+          <t>https://artportalen.se/Sighting/134480243</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123307520</v>
+        <v>134210232</v>
       </c>
       <c r="B43" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5358,19 +5359,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>567527</v>
+        <v>567573</v>
       </c>
       <c r="R43" t="n">
-        <v>6509582</v>
+        <v>6509528</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5397,27 +5402,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5444,13 +5434,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123307520</t>
+          <t>https://artportalen.se/Sighting/134210232</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127679939</v>
+        <v>123307520</v>
       </c>
       <c r="B44" t="n">
         <v>99195</v>
@@ -5480,7 +5470,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5497,10 +5487,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>567571</v>
+        <v>567527</v>
       </c>
       <c r="R44" t="n">
-        <v>6509585</v>
+        <v>6509582</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5545,6 +5535,11 @@
           <t>11:30</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5569,16 +5564,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127679939</t>
+          <t>https://artportalen.se/Sighting/123307520</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129866829</v>
+        <v>127679939</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,19 +5608,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>567588</v>
+        <v>567571</v>
       </c>
       <c r="R45" t="n">
-        <v>6509596</v>
+        <v>6509585</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5647,34 +5645,40 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5682,65 +5686,66 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129866829</t>
+          <t>https://artportalen.se/Sighting/127679939</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135331676</v>
+        <v>129866829</v>
       </c>
       <c r="B46" t="n">
-        <v>107785</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224272</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guldgul ängskovall</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. hians</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Druce</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>567573</v>
+        <v>567588</v>
       </c>
       <c r="R46" t="n">
-        <v>6509528</v>
+        <v>6509596</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5762,14 +5767,19 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,14 +5788,13 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -5793,8 +5802,119 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866829</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B47" t="n">
+        <v>107785</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135331676</t>
         </is>
@@ -5847,6 +5967,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>136274293</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>136274293</v>
       </c>
       <c r="B12" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
